--- a/publication_tables/main/table2.xlsx
+++ b/publication_tables/main/table2.xlsx
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.005</v>
+        <v>25.013</v>
       </c>
       <c r="C3" t="n">
-        <v>8.073</v>
+        <v>8.079000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>3.785</v>
+        <v>3.788</v>
       </c>
       <c r="E3" t="n">
         <v>0.401</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.909</v>
+        <v>-1.939</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.557</v>
+        <v>23.579</v>
       </c>
       <c r="C4" t="n">
-        <v>7.215</v>
+        <v>7.221</v>
       </c>
       <c r="D4" t="n">
-        <v>3.235</v>
+        <v>3.238</v>
       </c>
       <c r="E4" t="n">
         <v>0.395</v>
       </c>
       <c r="F4" t="n">
-        <v>2.262</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.052</v>
+        <v>24.086</v>
       </c>
       <c r="C5" t="n">
-        <v>7.338</v>
+        <v>7.344</v>
       </c>
       <c r="D5" t="n">
-        <v>3.289</v>
+        <v>3.292</v>
       </c>
       <c r="E5" t="n">
         <v>0.396</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1.078</v>
       </c>
     </row>
     <row r="6">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.441</v>
+        <v>24.453</v>
       </c>
       <c r="C6" t="n">
-        <v>7.725</v>
+        <v>7.732</v>
       </c>
       <c r="D6" t="n">
-        <v>3.559</v>
+        <v>3.562</v>
       </c>
       <c r="E6" t="n">
         <v>0.399</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.25</v>
+        <v>-0.282</v>
       </c>
     </row>
     <row r="7">
@@ -569,16 +569,16 @@
         <v>24.476</v>
       </c>
       <c r="C7" t="n">
-        <v>7.834</v>
+        <v>7.836</v>
       </c>
       <c r="D7" t="n">
-        <v>3.656</v>
+        <v>3.657</v>
       </c>
       <c r="E7" t="n">
         <v>0.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.703</v>
+        <v>-0.716</v>
       </c>
     </row>
   </sheetData>
@@ -592,114 +592,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Table 2. Distributional outcomes under the main configuration</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Note. Consumption is the money-metric change in real consumption relative to the benchmark, divided by initial expenditure. All supported policies have a net cost of 0.5% of benchmark GDP. Source: model simulations.</t>
+          <t>Policy scenario. Values follow the displayed precision of Table 2. Distributional outcomes under the main configuration. Full-precision simulation results accompany the analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FGT0 (%)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Poverty headcount, percent of represented persons. Values follow the displayed precision of Table 2. Distributional outcomes under the main configuration. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>FGT1 (%)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>FGT1 poverty-gap index, percent. Values follow the displayed precision of Table 2. Distributional outcomes under the main configuration. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>FGT2 (%)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Policy or reference equilibrium.</t>
+          <t>FGT2 squared poverty-gap index, percent. Values follow the displayed precision of Table 2. Distributional outcomes under the main configuration. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FGT0 (%)</t>
+          <t>Gini</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Poverty headcount: represented population below the fixed real poverty line (%).</t>
+          <t>Gini coefficient. Values follow the displayed precision of Table 2. Distributional outcomes under the main configuration. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FGT1 (%)</t>
+          <t>Bottom 40% consumption (%)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Poverty gap: normalised income shortfalls averaged over the whole population (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FGT2 (%)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Squared poverty gap: squared normalised shortfalls averaged over the whole population (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gini</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Gini coefficient of the reconstructed equivalent-income distribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Bottom 40% consumption (%)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Money-metric real consumption change for the benchmark bottom 40%, relative to initial expenditure (%).</t>
+          <t>Money-metric consumption change for the initial bottom 40 percent, as percent of their benchmark expenditure. Values follow the displayed precision of Table 2. Distributional outcomes under the main configuration. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
